--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{EE676F4B-BE0F-4CA0-92AA-B891C694F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{EAF8F34D-7B1B-4996-9D28-472FA2B0DB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -16,21 +16,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>username</t>
   </si>
@@ -75,6 +66,9 @@
   </si>
   <si>
     <t>shami@08</t>
+  </si>
+  <si>
+    <t>toji123@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -559,6 +553,9 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
@@ -576,8 +573,9 @@
     <hyperlink ref="A6" r:id="rId6" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
     <hyperlink ref="B6" r:id="rId7" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
     <hyperlink ref="B7" r:id="rId8" xr:uid="{A49E65D7-8AA3-4B9D-BC07-4CDF7ACB2B0E}"/>
+    <hyperlink ref="A7" r:id="rId9" xr:uid="{6C16F375-D6FB-4D81-9429-60C1A0E446A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId10"/>
 </worksheet>
 </file>
--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{EAF8F34D-7B1B-4996-9D28-472FA2B0DB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{5BB0956F-F29D-4B8E-A591-A6B1A1ED1739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>username</t>
   </si>
@@ -29,21 +29,12 @@
     <t>password</t>
   </si>
   <si>
-    <t>res</t>
-  </si>
-  <si>
     <t>lakshmi@yahoo.com</t>
   </si>
   <si>
-    <t>Lakshmi</t>
-  </si>
-  <si>
     <t>Valid</t>
   </si>
   <si>
-    <t>laksh@yahoo.com</t>
-  </si>
-  <si>
     <t>Laxmi</t>
   </si>
   <si>
@@ -69,6 +60,9 @@
   </si>
   <si>
     <t>toji123@gmail.com</t>
+  </si>
+  <si>
+    <t>result</t>
   </si>
 </sst>
 </file>
@@ -494,29 +488,29 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -524,7 +518,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -534,11 +528,11 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -546,36 +540,25 @@
         <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{D3BE7519-95C3-4ACD-9AB4-5385C9508082}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{8456409A-CACC-4B7E-B78E-75E713148E0E}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{94E9D5A6-98A1-4A25-BDDE-C5B20EDA887E}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
-    <hyperlink ref="B6" r:id="rId7" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
-    <hyperlink ref="B7" r:id="rId8" xr:uid="{A49E65D7-8AA3-4B9D-BC07-4CDF7ACB2B0E}"/>
-    <hyperlink ref="A7" r:id="rId9" xr:uid="{6C16F375-D6FB-4D81-9429-60C1A0E446A2}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{94E9D5A6-98A1-4A25-BDDE-C5B20EDA887E}"/>
+    <hyperlink ref="B2" r:id="rId3" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{A49E65D7-8AA3-4B9D-BC07-4CDF7ACB2B0E}"/>
+    <hyperlink ref="A6" r:id="rId7" xr:uid="{6C16F375-D6FB-4D81-9429-60C1A0E446A2}"/>
+    <hyperlink ref="A2" r:id="rId8" xr:uid="{D3BE7519-95C3-4ACD-9AB4-5385C9508082}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId10"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
 </worksheet>
 </file>
--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{5BB0956F-F29D-4B8E-A591-A6B1A1ED1739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F30B9604-FE56-49E7-A902-ABB51DFE65FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -510,7 +510,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
